--- a/data/WP18/WP18_auswertung_ministerien.xlsx
+++ b/data/WP18/WP18_auswertung_ministerien.xlsx
@@ -749,23 +749,39 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="s">
+      <c r="A16"/>
+      <c r="B16"/>
+      <c r="C16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
         <v>34</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B17" t="s">
         <v>35</v>
       </c>
-      <c r="C16" t="n">
-        <v>7341</v>
-      </c>
-      <c r="D16" t="n">
+      <c r="C17" t="n">
+        <v>7342</v>
+      </c>
+      <c r="D17" t="n">
         <v>35.9313445034737</v>
       </c>
-      <c r="E16" t="n">
+      <c r="E17" t="n">
         <v>5552</v>
       </c>
-      <c r="F16" t="n">
-        <v>24.369976842392</v>
+      <c r="F17" t="n">
+        <v>24.3802778534459</v>
       </c>
     </row>
   </sheetData>
@@ -1002,13 +1018,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAB6548F-89FF-43AE-8A8E-FFA3277A0060}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BBC9B435-D2A1-4358-AF75-37CED477C274}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{05681C18-8C03-4A4E-AD39-0B3D355CBCCE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8C30C077-C6E4-4F53-99A4-C48C8D57AECF}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D36BB31A-6617-4AB7-AD8D-78A37F32255F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DE5D3B72-8B4D-4098-A166-5B949FB30D64}"/>
 </file>
--- a/data/WP18/WP18_auswertung_ministerien.xlsx
+++ b/data/WP18/WP18_auswertung_ministerien.xlsx
@@ -479,13 +479,13 @@
         <v>1599</v>
       </c>
       <c r="D2" t="n">
-        <v>37.5966228893059</v>
+        <v>37.6873045653533</v>
       </c>
       <c r="E2" t="n">
-        <v>1332</v>
+        <v>1327</v>
       </c>
       <c r="F2" t="n">
-        <v>16.6979362101313</v>
+        <v>17.010631644778</v>
       </c>
     </row>
     <row r="3">
@@ -496,16 +496,16 @@
         <v>9</v>
       </c>
       <c r="C3" t="n">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="D3" t="n">
-        <v>36.5689338235294</v>
+        <v>36.3489439853076</v>
       </c>
       <c r="E3" t="n">
-        <v>884</v>
+        <v>873</v>
       </c>
       <c r="F3" t="n">
-        <v>18.75</v>
+        <v>19.8347107438017</v>
       </c>
     </row>
     <row r="4">
@@ -519,13 +519,13 @@
         <v>920</v>
       </c>
       <c r="D4" t="n">
-        <v>40.3739130434782</v>
+        <v>40.0652173913043</v>
       </c>
       <c r="E4" t="n">
-        <v>805</v>
+        <v>798</v>
       </c>
       <c r="F4" t="n">
-        <v>12.5</v>
+        <v>13.2608695652174</v>
       </c>
     </row>
     <row r="5">
@@ -539,13 +539,13 @@
         <v>730</v>
       </c>
       <c r="D5" t="n">
-        <v>33.7698630136986</v>
+        <v>32.9315068493151</v>
       </c>
       <c r="E5" t="n">
-        <v>517</v>
+        <v>454</v>
       </c>
       <c r="F5" t="n">
-        <v>29.1780821917808</v>
+        <v>37.8082191780822</v>
       </c>
     </row>
     <row r="6">
@@ -559,13 +559,13 @@
         <v>701</v>
       </c>
       <c r="D6" t="n">
-        <v>33.095577746077</v>
+        <v>32.6847360912981</v>
       </c>
       <c r="E6" t="n">
-        <v>387</v>
+        <v>377</v>
       </c>
       <c r="F6" t="n">
-        <v>44.793152639087</v>
+        <v>46.2196861626248</v>
       </c>
     </row>
     <row r="7">
@@ -579,13 +579,13 @@
         <v>590</v>
       </c>
       <c r="D7" t="n">
-        <v>32.493220338983</v>
+        <v>32.2305084745763</v>
       </c>
       <c r="E7" t="n">
-        <v>404</v>
+        <v>384</v>
       </c>
       <c r="F7" t="n">
-        <v>31.5254237288136</v>
+        <v>34.9152542372881</v>
       </c>
     </row>
     <row r="8">
@@ -599,13 +599,13 @@
         <v>390</v>
       </c>
       <c r="D8" t="n">
-        <v>34.1717948717949</v>
+        <v>30.6076923076923</v>
       </c>
       <c r="E8" t="n">
-        <v>272</v>
+        <v>227</v>
       </c>
       <c r="F8" t="n">
-        <v>30.2564102564103</v>
+        <v>41.7948717948718</v>
       </c>
     </row>
     <row r="9">
@@ -619,13 +619,13 @@
         <v>374</v>
       </c>
       <c r="D9" t="n">
-        <v>37.692513368984</v>
+        <v>37.5935828877005</v>
       </c>
       <c r="E9" t="n">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F9" t="n">
-        <v>23.7967914438503</v>
+        <v>24.0641711229947</v>
       </c>
     </row>
     <row r="10">
@@ -639,13 +639,13 @@
         <v>335</v>
       </c>
       <c r="D10" t="n">
-        <v>35.5761194029851</v>
+        <v>35.1313432835821</v>
       </c>
       <c r="E10" t="n">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="F10" t="n">
-        <v>24.7761194029851</v>
+        <v>26.865671641791</v>
       </c>
     </row>
     <row r="11">
@@ -659,13 +659,13 @@
         <v>294</v>
       </c>
       <c r="D11" t="n">
-        <v>33.8571428571429</v>
+        <v>33.6666666666667</v>
       </c>
       <c r="E11" t="n">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="F11" t="n">
-        <v>23.1292517006803</v>
+        <v>25.1700680272109</v>
       </c>
     </row>
     <row r="12">
@@ -679,13 +679,13 @@
         <v>197</v>
       </c>
       <c r="D12" t="n">
-        <v>32.7918781725888</v>
+        <v>31.5482233502538</v>
       </c>
       <c r="E12" t="n">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="F12" t="n">
-        <v>44.1624365482233</v>
+        <v>49.746192893401</v>
       </c>
     </row>
     <row r="13">
@@ -699,13 +699,13 @@
         <v>117</v>
       </c>
       <c r="D13" t="n">
-        <v>32.008547008547</v>
+        <v>29.7606837606838</v>
       </c>
       <c r="E13" t="n">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="F13" t="n">
-        <v>35.042735042735</v>
+        <v>47.8632478632479</v>
       </c>
     </row>
     <row r="14">
@@ -719,7 +719,7 @@
         <v>4</v>
       </c>
       <c r="D14" t="n">
-        <v>28.25</v>
+        <v>26.5</v>
       </c>
       <c r="E14" t="n">
         <v>1</v>
@@ -749,39 +749,23 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16"/>
-      <c r="B16"/>
+      <c r="A16" t="s">
+        <v>34</v>
+      </c>
+      <c r="B16" t="s">
+        <v>35</v>
+      </c>
       <c r="C16" t="n">
-        <v>1</v>
-      </c>
-      <c r="D16" t="e">
-        <v>#NUM!</v>
+        <v>7342</v>
+      </c>
+      <c r="D16" t="n">
+        <v>35.4437482974669</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>5351</v>
       </c>
       <c r="F16" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="s">
-        <v>34</v>
-      </c>
-      <c r="B17" t="s">
-        <v>35</v>
-      </c>
-      <c r="C17" t="n">
-        <v>7342</v>
-      </c>
-      <c r="D17" t="n">
-        <v>35.9313445034737</v>
-      </c>
-      <c r="E17" t="n">
-        <v>5552</v>
-      </c>
-      <c r="F17" t="n">
-        <v>24.3802778534459</v>
+        <v>27.1179515118496</v>
       </c>
     </row>
   </sheetData>
@@ -1018,13 +1002,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BBC9B435-D2A1-4358-AF75-37CED477C274}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{56932A89-E704-4269-AFC1-F16C39C040D1}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8C30C077-C6E4-4F53-99A4-C48C8D57AECF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{03EC633B-5DC4-4F55-9A49-F68EE5960131}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DE5D3B72-8B4D-4098-A166-5B949FB30D64}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8294B2B4-4E22-48D4-8100-B9D07DE5EADE}"/>
 </file>
--- a/data/WP18/WP18_auswertung_ministerien.xlsx
+++ b/data/WP18/WP18_auswertung_ministerien.xlsx
@@ -482,10 +482,10 @@
         <v>37.6873045653533</v>
       </c>
       <c r="E2" t="n">
-        <v>1327</v>
+        <v>1393</v>
       </c>
       <c r="F2" t="n">
-        <v>17.010631644778</v>
+        <v>12.8830519074422</v>
       </c>
     </row>
     <row r="3">
@@ -502,10 +502,10 @@
         <v>36.3489439853076</v>
       </c>
       <c r="E3" t="n">
-        <v>873</v>
+        <v>912</v>
       </c>
       <c r="F3" t="n">
-        <v>19.8347107438017</v>
+        <v>16.2534435261708</v>
       </c>
     </row>
     <row r="4">
@@ -522,10 +522,10 @@
         <v>40.0652173913043</v>
       </c>
       <c r="E4" t="n">
-        <v>798</v>
+        <v>829</v>
       </c>
       <c r="F4" t="n">
-        <v>13.2608695652174</v>
+        <v>9.89130434782609</v>
       </c>
     </row>
     <row r="5">
@@ -542,10 +542,10 @@
         <v>32.9315068493151</v>
       </c>
       <c r="E5" t="n">
-        <v>454</v>
+        <v>532</v>
       </c>
       <c r="F5" t="n">
-        <v>37.8082191780822</v>
+        <v>27.1232876712329</v>
       </c>
     </row>
     <row r="6">
@@ -562,10 +562,10 @@
         <v>32.6847360912981</v>
       </c>
       <c r="E6" t="n">
-        <v>377</v>
+        <v>423</v>
       </c>
       <c r="F6" t="n">
-        <v>46.2196861626248</v>
+        <v>39.6576319543509</v>
       </c>
     </row>
     <row r="7">
@@ -582,10 +582,10 @@
         <v>32.2305084745763</v>
       </c>
       <c r="E7" t="n">
-        <v>384</v>
+        <v>453</v>
       </c>
       <c r="F7" t="n">
-        <v>34.9152542372881</v>
+        <v>23.2203389830509</v>
       </c>
     </row>
     <row r="8">
@@ -602,10 +602,10 @@
         <v>30.6076923076923</v>
       </c>
       <c r="E8" t="n">
-        <v>227</v>
+        <v>261</v>
       </c>
       <c r="F8" t="n">
-        <v>41.7948717948718</v>
+        <v>33.0769230769231</v>
       </c>
     </row>
     <row r="9">
@@ -622,10 +622,10 @@
         <v>37.5935828877005</v>
       </c>
       <c r="E9" t="n">
-        <v>284</v>
+        <v>302</v>
       </c>
       <c r="F9" t="n">
-        <v>24.0641711229947</v>
+        <v>19.2513368983957</v>
       </c>
     </row>
     <row r="10">
@@ -642,10 +642,10 @@
         <v>35.1313432835821</v>
       </c>
       <c r="E10" t="n">
-        <v>245</v>
+        <v>272</v>
       </c>
       <c r="F10" t="n">
-        <v>26.865671641791</v>
+        <v>18.8059701492537</v>
       </c>
     </row>
     <row r="11">
@@ -662,10 +662,10 @@
         <v>33.6666666666667</v>
       </c>
       <c r="E11" t="n">
-        <v>220</v>
+        <v>241</v>
       </c>
       <c r="F11" t="n">
-        <v>25.1700680272109</v>
+        <v>18.0272108843537</v>
       </c>
     </row>
     <row r="12">
@@ -682,10 +682,10 @@
         <v>31.5482233502538</v>
       </c>
       <c r="E12" t="n">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="F12" t="n">
-        <v>49.746192893401</v>
+        <v>45.6852791878173</v>
       </c>
     </row>
     <row r="13">
@@ -702,10 +702,10 @@
         <v>29.7606837606838</v>
       </c>
       <c r="E13" t="n">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="F13" t="n">
-        <v>47.8632478632479</v>
+        <v>40.1709401709402</v>
       </c>
     </row>
     <row r="14">
@@ -762,10 +762,10 @@
         <v>35.4437482974669</v>
       </c>
       <c r="E16" t="n">
-        <v>5351</v>
+        <v>5797</v>
       </c>
       <c r="F16" t="n">
-        <v>27.1179515118496</v>
+        <v>21.043312448924</v>
       </c>
     </row>
   </sheetData>
@@ -1002,13 +1002,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{56932A89-E704-4269-AFC1-F16C39C040D1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A2FFB74-5FE6-4D1E-87C9-387E124AC5FA}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{03EC633B-5DC4-4F55-9A49-F68EE5960131}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C184FB14-702F-4D97-A1BB-CC63C93D6278}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8294B2B4-4E22-48D4-8100-B9D07DE5EADE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{337692EB-B75E-4025-98B7-3F18DA95E207}"/>
 </file>